--- a/src/ii_skills/shared/excel_templates/06_before_after.xlsx
+++ b/src/ii_skills/shared/excel_templates/06_before_after.xlsx
@@ -29,14 +29,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="0001395D"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -45,18 +46,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A4A4A"/>
-        <bgColor rgb="004A4A4A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-        <bgColor rgb="00F0F0F0"/>
+        <fgColor rgb="0001395D"/>
+        <bgColor rgb="0001395D"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -64,28 +59,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,178 +436,142 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1"/>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Value-Add Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Before_Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>After_Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Change_Pct</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Change_Abs</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>KPI Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Before</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Change $</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="C5" s="3" t="n">
         <v>2780</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="D5" s="3" t="n">
         <v>5087</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="F5" s="3" t="n">
         <v>2307</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>$5,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Rent per Unit</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
+      <c r="C6" s="3" t="n">
         <v>2780</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="D6" s="3" t="n">
         <v>3395</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.22</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="F6" s="3" t="n">
         <v>615</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Uplift</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>+$400/month</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Care Revenue</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="D7" s="3" t="n">
         <v>1692</v>
       </c>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="4" t="n">
+      <c r="F7" s="3" t="n">
         <v>1692</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Payback</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1 Year</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="C8" t="n">
         <v>0.85</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="D8" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.11</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F8" t="n">
         <v>0.09</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ROI</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>NOI Margin</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="C9" t="n">
         <v>0.35</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D9" t="n">
         <v>0.42</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F9" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
